--- a/AAII_Financials/Quarterly/CTPCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTPCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>CTPCY</t>
   </si>
@@ -656,71 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -763,8 +769,14 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +819,14 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -851,8 +869,14 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -869,8 +893,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -913,8 +939,14 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -957,8 +989,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1001,8 +1039,14 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1045,8 +1089,14 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1060,8 +1110,10 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1104,8 +1156,14 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,8 +1206,14 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1166,8 +1230,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1210,8 +1276,14 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1254,8 +1326,14 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1298,8 +1376,14 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1342,8 +1426,14 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1386,8 +1476,14 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1430,8 +1526,14 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1474,8 +1576,14 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1518,8 +1626,14 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1562,8 +1676,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1606,8 +1726,14 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1650,8 +1776,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1694,8 +1826,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1738,8 +1876,14 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1782,8 +1926,14 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1826,8 +1976,14 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1870,57 +2026,69 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1937,8 +2105,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1955,404 +2125,460 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>613400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>604100</v>
+      </c>
+      <c r="F41" s="3">
         <v>644700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>600000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>592300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>712400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>576900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>580600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>635200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>635200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>617300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>568800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>600500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>812500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>787700</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>347633100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>342361200</v>
+      </c>
+      <c r="F42" s="3">
         <v>320144700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>303612600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>299734000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>288980800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>255079900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>256719100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>248206600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>248206600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>241209300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>236637900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>249835400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>227961500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>221005000</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>918305400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>904379200</v>
+      </c>
+      <c r="F43" s="3">
         <v>873149500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>839430200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>828706700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>809832700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>788769800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>793838500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>800620400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>800620400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>778049900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>752943600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>794935800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>753524800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>730530200</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16883000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>16627000</v>
+      </c>
+      <c r="F44" s="3">
         <v>16969100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>17129500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>16910600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>16938700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>17662300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>17775800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>19058500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>19058500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>18521200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>16029400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>16923400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>15810800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>15328300</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>146351600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>144132100</v>
+      </c>
+      <c r="F45" s="3">
         <v>111161100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>91016400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>89853600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>81225500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>64750200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>65166300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>61478700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>61478700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>59745500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>71904500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>75914700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>62753900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>60838900</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1524856300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1501731700</v>
+      </c>
+      <c r="F46" s="3">
         <v>1395386200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1323630300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1306721300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1260025200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1198047900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1205746700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1205678800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1205678800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1171689300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1156840600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1221358400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1144486200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1109561000</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>387530600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>381653700</v>
+      </c>
+      <c r="F47" s="3">
         <v>373152000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>337243900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>332935700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>316809700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>298696600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>300616000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>314604600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>314604600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>305735500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>287659400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>303702300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>314944900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>305334000</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43260700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>42604600</v>
+      </c>
+      <c r="F48" s="3">
         <v>41825900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>39317800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>38815500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>36626000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>35916600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>36147400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>36968900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>36968900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>35926700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>29198600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>30827000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>29145600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>28256200</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7171900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7063100</v>
+      </c>
+      <c r="F49" s="3">
         <v>7064100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>6714200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>6628400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>6765800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>6692000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6735000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>6855700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>6855700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>6662400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>6282800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>6633200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>6138900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>5951500</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2395,8 +2621,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2439,52 +2671,64 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>35212600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>34678600</v>
+      </c>
+      <c r="F52" s="3">
         <v>31780000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>25366300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>25042200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>22503600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>22492300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>22636800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>22093000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>22093000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>21470100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>21601000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>22805700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>20857900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>20221400</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2527,52 +2771,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2009938500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1979457500</v>
+      </c>
+      <c r="F54" s="3">
         <v>1861652200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1744232100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1721950000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1654371800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1572784000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1582890900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1597952300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1597952300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1552904100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1513493000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1597901500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1528452600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1481810300</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2589,8 +2845,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2607,272 +2865,310 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15950900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>15709000</v>
+      </c>
+      <c r="F57" s="3">
         <v>15139700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>14318400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>14135500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>14554000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>14666900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>14761200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>15953400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>15953400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>15503700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>12961000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>13683800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>13089100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>12689700</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>270946700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>266837800</v>
+      </c>
+      <c r="F58" s="3">
         <v>334808000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>294691500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>290926900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>281213600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>234938400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>236448200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>253909100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>253909100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>246751100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>177898200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>187819700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>216186300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>209589100</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>550360200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>542013900</v>
+      </c>
+      <c r="F59" s="3">
         <v>490914600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>767122300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>757322500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>472395000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>469572300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>472589800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>485181000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>485181000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>471503200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>502434100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>530455200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>499759300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>484508700</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>847277400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>834428300</v>
+      </c>
+      <c r="F60" s="3">
         <v>853532100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1089035400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1075123300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>781364700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>731461800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>736162300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>766157600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>766157600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>744558700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>702719400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>741910600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>739170100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>716613600</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>148957300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>146698300</v>
+      </c>
+      <c r="F61" s="3">
         <v>109720500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>119557800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>118030500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>94851700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>125450100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>126256200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>122574400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>122574400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>119118900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>109543000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>115652300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>85161200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>82562400</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>768646700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>756990000</v>
+      </c>
+      <c r="F62" s="3">
         <v>670424100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>318395500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>314328100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>570016000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>509463500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>512737300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>505868900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>505868900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>491607900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>511128200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>539634200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>510213000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>494643300</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2915,8 +3211,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2959,8 +3261,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3003,52 +3311,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1778490300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1751519300</v>
+      </c>
+      <c r="F66" s="3">
         <v>1647672300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1540317400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1520640300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1459414300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1379431000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1388295400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1409431500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1409431500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1369697900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1337524800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1412119500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1349441200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1308261700</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3065,8 +3385,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3109,8 +3431,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3153,8 +3481,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3197,8 +3531,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3241,52 +3581,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>79959200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>78746600</v>
+      </c>
+      <c r="F72" s="3">
         <v>74406500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>69685600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>68795400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>65625500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>63057700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>63462900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>61465800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>61465800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>59733000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>57379700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>60579800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>57311800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>55562900</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3329,8 +3681,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3373,8 +3731,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3417,52 +3781,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>117880400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>116092700</v>
+      </c>
+      <c r="F76" s="3">
         <v>111853600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>106742200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>105378600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>103778100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>100934600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>101583300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>99166300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>99166300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>96370600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>94399400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>99664200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>95706800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>92786200</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3505,57 +3881,69 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3598,8 +3986,14 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3616,52 +4010,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>775600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3166100</v>
+      </c>
+      <c r="F83" s="3">
         <v>750700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>755500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>667300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>648500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>654800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>691300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>785600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>785600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>761600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>606600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>640900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>622900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>623900</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3704,8 +4106,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3748,8 +4156,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3792,8 +4206,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3836,8 +4256,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3880,52 +4306,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18756300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>18471900</v>
+      </c>
+      <c r="F89" s="3">
         <v>23175400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>2351400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2321400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5689700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-20364800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-20495700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>7722200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>7722200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>7504500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-9122100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-9630900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>11119700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>10780400</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3942,52 +4380,60 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1305700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1285900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2928300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-2101400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2074600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2171800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-776200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-781200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1049600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-619600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-654200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1126200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1091800</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4030,8 +4476,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4074,52 +4526,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2566100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2527200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-12685300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-9852200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-9726300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-13383200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>1365700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>1374500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-4584600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4584600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-4455400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>1843400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>1946200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-8774600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-8506800</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4136,8 +4600,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4159,29 +4625,35 @@
       <c r="I96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>1219900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>1219900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>1185500</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3">
         <v>1189200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>1152900</v>
       </c>
     </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4224,8 +4696,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4268,8 +4746,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4312,136 +4796,160 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5961000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-5870600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-12386600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>7204800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>7112700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>4707200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>16014300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>16117200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-3002400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-3002400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2917700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2173200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>2294400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2524700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-2447700</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-217500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>715600</v>
+      </c>
+      <c r="F101" s="3">
         <v>178500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>179700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>76800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>74600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>180700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>190800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>470400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>470400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>456100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>355600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>375800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>190700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>191000</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9747300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>9599500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2443000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-516300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-509700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2270700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2806200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2824300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>212000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>212000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>206100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-4924900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-5199500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>290800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>282000</v>
       </c>
     </row>
